--- a/assets/files/sistem_penggajian2.xlsx
+++ b/assets/files/sistem_penggajian2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEEDDCDE-60A2-4A66-916D-503516DFC4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496A4EDE-DDA7-4CBB-9318-2203AEB783EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E37C903E-9C6B-470E-B6C6-238D4DBCD395}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="34">
   <si>
     <t>Kode Golongan</t>
   </si>
@@ -126,6 +126,18 @@
   </si>
   <si>
     <t>TABEL DATA KARYAWAN</t>
+  </si>
+  <si>
+    <t>lll</t>
+  </si>
+  <si>
+    <t>Penggunaan IFERROR</t>
+  </si>
+  <si>
+    <t>Penggunaan VLOOKUP </t>
+  </si>
+  <si>
+    <t>Menampilkan ERROR typo dan Golongan tidak ditemukan</t>
   </si>
 </sst>
 </file>
@@ -133,9 +145,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,8 +177,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF212529"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -175,13 +207,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -325,7 +369,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -336,28 +380,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -369,7 +395,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -706,13 +811,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7DAC380-6B50-4244-970D-8E7507EADD25}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="1"/>
     <col min="6" max="7" width="17.28515625" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.140625" style="1"/>
@@ -721,377 +826,575 @@
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="7"/>
-      <c r="F1" s="5" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
+      <c r="F2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="7"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="G2" s="16"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G3" s="19" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="11">
-        <f>VLOOKUP(C3,$F$3:$G$7,2,)</f>
+      <c r="D4" s="5">
+        <f t="shared" ref="D4:D11" si="0">VLOOKUP(C4,$F$4:$G$8,2,)</f>
         <v>9000000</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G4" s="5">
         <v>5000000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="11">
-        <f>VLOOKUP(C4,$F$3:$G$7,2,)</f>
+      <c r="D5" s="5">
+        <f t="shared" si="0"/>
         <v>7000000</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G5" s="5">
         <v>7000000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="11">
-        <f>VLOOKUP(C5,$F$3:$G$7,2,)</f>
+      <c r="D6" s="5">
+        <f t="shared" si="0"/>
         <v>15000000</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G6" s="5">
         <v>9000000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="11">
-        <f>VLOOKUP(C6,$F$3:$G$7,2,)</f>
+      <c r="D7" s="5">
+        <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G7" s="5">
         <v>12000000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="11">
-        <f>VLOOKUP(C7,$F$3:$G$7,2,)</f>
+      <c r="D8" s="5">
+        <f t="shared" si="0"/>
         <v>12000000</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G8" s="9">
         <v>15000000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="11">
-        <f>VLOOKUP(C8,$F$3:$G$7,2,)</f>
+      <c r="D9" s="5">
+        <f t="shared" si="0"/>
         <v>9000000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="11" t="e">
-        <f>VLOOKUP(C9,$F$3:$G$7,2,)</f>
+      <c r="D10" s="5" t="e">
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="15" t="e">
-        <f>VLOOKUP(C10,$F$3:$G$7,2,)</f>
+      <c r="D11" s="9" t="e">
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="F13" s="5" t="s">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
+      <c r="F14" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B15" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C15" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D15" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F15" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G15" s="22" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="11">
-        <f>VLOOKUP(C15,$F$3:$G$7,2,)</f>
+      <c r="D16" s="5">
+        <f>IFERROR(VLOOKUP(C16,$F$16:$G$20,2,FALSE),"Golongan tidak ditemukan")</f>
         <v>9000000</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F16" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G16" s="5">
         <v>5000000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="11">
-        <f>VLOOKUP(C16,$F$3:$G$7,2,)</f>
+      <c r="D17" s="5">
+        <f t="shared" ref="D17:D23" si="1">IFERROR(VLOOKUP(C17,$F$16:$G$20,2,FALSE),"Golongan tidak ditemukan")</f>
         <v>7000000</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F17" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G17" s="5">
         <v>7000000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="11">
-        <f>VLOOKUP(C17,$F$3:$G$7,2,)</f>
+      <c r="D18" s="5">
+        <f t="shared" si="1"/>
         <v>15000000</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F18" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G18" s="5">
         <v>9000000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="11">
-        <f>VLOOKUP(C18,$F$3:$G$7,2,)</f>
+      <c r="D19" s="5">
+        <f t="shared" si="1"/>
         <v>5000000</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F19" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G19" s="5">
         <v>12000000</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="11">
-        <f>VLOOKUP(C19,$F$3:$G$7,2,)</f>
+      <c r="D20" s="5">
+        <f t="shared" si="1"/>
         <v>12000000</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G20" s="9">
         <v>15000000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="11">
-        <f>VLOOKUP(C20,$F$3:$G$7,2,)</f>
+      <c r="D21" s="5">
+        <f t="shared" si="1"/>
         <v>9000000</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="11" t="e">
-        <f>VLOOKUP(C21,$F$3:$G$7,2,)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
+      <c r="C22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Golongan tidak ditemukan</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B23" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C23" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="15" t="e">
-        <f>VLOOKUP(C22,$F$3:$G$7,2,)</f>
-        <v>#N/A</v>
+      <c r="D23" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Golongan tidak ditemukan</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="25"/>
+      <c r="F26" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="25"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="32">
+        <f>IF(COUNTIF($F$28:$G$32,C28)=0,"Golongan '"&amp;C28&amp;"' tidak ditemukan",VLOOKUP(C28,$F$28:$G$32,2,FALSE))</f>
+        <v>9000000</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="32">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="32">
+        <f t="shared" ref="D29:D35" si="2">IF(COUNTIF($F$28:$G$32,C29)=0,"Golongan '"&amp;C29&amp;"' tidak ditemukan",VLOOKUP(C29,$F$28:$G$32,2,FALSE))</f>
+        <v>7000000</v>
+      </c>
+      <c r="F29" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="32">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="32">
+        <f t="shared" si="2"/>
+        <v>15000000</v>
+      </c>
+      <c r="F30" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" s="32">
+        <v>9000000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="32">
+        <f t="shared" si="2"/>
+        <v>5000000</v>
+      </c>
+      <c r="F31" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="G31" s="32">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="32">
+        <f t="shared" si="2"/>
+        <v>12000000</v>
+      </c>
+      <c r="F32" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="36">
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="32">
+        <f t="shared" si="2"/>
+        <v>9000000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>Golongan 'lll' tidak ditemukan</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Golongan 'VI' tidak ditemukan</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F13:G13"/>
+  <mergeCells count="6">
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="F26:G26"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
